--- a/scratch/paper_figs/compare_Si_vs_ITO_data.xlsx
+++ b/scratch/paper_figs/compare_Si_vs_ITO_data.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Si nFET" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="OSFET" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si nFET" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSFET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8063,7 +8063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8089,75 +8089,115 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>ID0 (A)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>idx_off</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>idx_on</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>off_slope</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>on_slope</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>off_intercept</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>on_intercept</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>on_ylabel</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>VTR_deriv_gm_over_cgg (V)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>VTR_deriv_gm (V)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>VT_gm_by_id (V)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>VT_gm_by_cgg (V)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>VT_gm (V)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>window_length</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>polyorder</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>npts_fit</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>off_frac</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>on_frac</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>VOV_limit</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ID_limit</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>trough_frac</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>peak_frac</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>slope_window</t>
         </is>
@@ -8179,48 +8219,74 @@
         <v>0.08269849318513617</v>
       </c>
       <c r="E2" t="n">
+        <v>1.834900922025691e-07</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12.35894397025218</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.238679999999993e-05</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-12.51663705539856</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-1.37217466666666e-05</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>I_D (raw)</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>0.07517627153017092</v>
       </c>
-      <c r="F2" t="n">
+      <c r="N2" t="n">
         <v>0.119492628765396</v>
       </c>
-      <c r="G2" t="n">
+      <c r="O2" t="n">
         <v>0.4876832295640644</v>
       </c>
-      <c r="H2" t="n">
+      <c r="P2" t="n">
         <v>0.5628595010942353</v>
       </c>
-      <c r="I2" t="n">
+      <c r="Q2" t="n">
         <v>0.6071758583294604</v>
       </c>
-      <c r="J2" t="n">
+      <c r="R2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="S2" t="n">
         <v>3</v>
       </c>
-      <c r="L2" t="n">
+      <c r="T2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="U2" t="n">
         <v>0.001</v>
       </c>
-      <c r="N2" t="n">
+      <c r="V2" t="n">
         <v>0.2</v>
       </c>
-      <c r="O2" t="n">
+      <c r="W2" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="n">
+      <c r="X2" t="n">
         <v>2e-12</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Y2" t="n">
         <v>0.9</v>
       </c>
-      <c r="R2" t="n">
+      <c r="Z2" t="n">
         <v>0.5</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AA2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -8240,48 +8306,74 @@
         <v>0.7374361609411244</v>
       </c>
       <c r="E3" t="n">
+        <v>3.927110812779629e-07</v>
+      </c>
+      <c r="F3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G3" t="n">
+        <v>144</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16.15841271120369</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.784000000000044e-05</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-10.39150501785014</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-3.809533333333451e-05</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>I_D (raw)</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>0.6758975904314943</v>
       </c>
-      <c r="F3" t="n">
+      <c r="N3" t="n">
         <v>0.6908516440968973</v>
       </c>
-      <c r="G3" t="n">
+      <c r="O3" t="n">
         <v>0.187206514711453</v>
       </c>
-      <c r="H3" t="n">
+      <c r="P3" t="n">
         <v>0.8631041051429473</v>
       </c>
-      <c r="I3" t="n">
+      <c r="Q3" t="n">
         <v>0.8780581588083503</v>
       </c>
-      <c r="J3" t="n">
+      <c r="R3" t="n">
         <v>5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="S3" t="n">
         <v>3</v>
       </c>
-      <c r="L3" t="n">
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
+      <c r="U3" t="n">
         <v>0.001</v>
       </c>
-      <c r="N3" t="n">
+      <c r="V3" t="n">
         <v>0.2</v>
       </c>
-      <c r="O3" t="n">
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="P3" t="n">
+      <c r="X3" t="n">
         <v>2e-12</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Y3" t="n">
         <v>0.9</v>
       </c>
-      <c r="R3" t="n">
+      <c r="Z3" t="n">
         <v>0.5</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AA3" t="n">
         <v>21</v>
       </c>
     </row>
